--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T10:14:30+00:00</t>
+    <t>2025-05-12T19:48:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:50:51+00:00</t>
+    <t>2025-05-12T19:54:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T19:54:00+00:00</t>
+    <t>2025-05-13T10:14:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-13T10:14:10+00:00</t>
+    <t>2025-05-14T06:55:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T06:55:09+00:00</t>
+    <t>2025-05-14T07:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:28:26+00:00</t>
+    <t>2025-05-14T07:30:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:30:17+00:00</t>
+    <t>2025-05-14T07:51:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T07:51:32+00:00</t>
+    <t>2025-05-14T08:54:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T08:54:50+00:00</t>
+    <t>2025-05-14T13:37:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:37:41+00:00</t>
+    <t>2025-05-14T14:59:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
+++ b/branches/cpg-profiles/StructureDefinition-PSSPatient.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:59:57+00:00</t>
+    <t>2025-05-14T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
